--- a/Cell survival results/2026_3_18/Multiplicity X-ray 18-3.xlsx
+++ b/Cell survival results/2026_3_18/Multiplicity X-ray 18-3.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="231" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7077CA1E-4548-4130-B83D-46FEDF9D38D6}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bhaan\Documents\#Master Degree\Thesis\Thesis_project\Cell survival results\2026_3_18\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BC5530-ABE8-4F5C-A597-406EED27534D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>Sample</t>
   </si>
@@ -61,17 +66,13 @@
   </si>
   <si>
     <t>B6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -108,12 +109,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -448,10 +446,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -468,7 +466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -482,11 +480,11 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <f>SUM(B2:D2)</f>
+        <f t="shared" ref="E2:E9" si="0">SUM(B2:D2)</f>
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -500,11 +498,11 @@
         <v>2</v>
       </c>
       <c r="E3">
-        <f>SUM(B3:D3)</f>
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -518,11 +516,11 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <f>SUM(B4:D4)</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -536,11 +534,11 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <f>SUM(B5:D5)</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -554,11 +552,11 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <f>SUM(B6:D6)</f>
+        <f t="shared" si="0"/>
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -572,11 +570,11 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <f>SUM(B7:D7)</f>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -590,11 +588,11 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <f>SUM(B8:D8)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -608,11 +606,11 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <f>SUM(B9:D9)</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
@@ -631,11 +629,6 @@
       <c r="E10">
         <f>SUM(E2:E9)</f>
         <v>331</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="29.25">
-      <c r="B11" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
